--- a/data/trans_orig/IP31KM07_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP31KM07_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>109498</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>100261</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>116117</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>89,1%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>81,58%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>94,48%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>174</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>104416</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>98440</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>108820</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>91,39%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>86,16%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>95,25%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>116852</t>
+          <t>108774</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>99183</t>
+          <t>102652</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>126466</t>
+          <t>113258</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>85,41%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,49%</t>
+          <t>86,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>95,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>221268</t>
+          <t>218272</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>199530</t>
+          <t>207816</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>231402</t>
+          <t>226152</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>88,13%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>79,47%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>93,65%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>13398</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>6779</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>22635</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>10,9%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5,52%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>18,42%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>9835</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>5431</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>15811</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>8,61%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4,75%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>13,84%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>19963</t>
+          <t>9824</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10349</t>
+          <t>5340</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37632</t>
+          <t>15946</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,59%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,51%</t>
+          <t>13,45%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>29798</t>
+          <t>23222</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19664</t>
+          <t>15342</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51536</t>
+          <t>33678</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>9,62%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>20,53%</t>
+          <t>13,95%</t>
         </is>
       </c>
     </row>
@@ -946,57 +946,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>122896</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>136815</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>251066</t>
+          <t>241494</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1063,74 +1063,74 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>205057</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>187856</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>213577</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>88,68%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>81,24%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>92,36%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>248</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>173080</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>166231</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>177969</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>93,0%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>89,32%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>167628</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>160781</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>172687</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>92,82%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>89,03%</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
         <is>
           <t>95,62%</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>291</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>216604</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>197344</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>226484</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>87,51%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>79,73%</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>91,5%</t>
-        </is>
-      </c>
       <c r="Q7" s="2" t="inlineStr">
         <is>
           <t>539</t>
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>389684</t>
+          <t>372684</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>370118</t>
+          <t>358043</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>400923</t>
+          <t>383083</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>89,86%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>92,46%</t>
+          <t>93,02%</t>
         </is>
       </c>
     </row>
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>26184</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>17664</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>43385</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>11,32%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>18,76%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>21</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>13034</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>8145</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>19883</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>7,0%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>12965</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>7906</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>19812</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>7,18%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>4,38%</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>10,68%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>30916</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>21036</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>50176</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>12,49%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>8,5%</t>
-        </is>
-      </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>43950</t>
+          <t>39149</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>32711</t>
+          <t>28750</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>63516</t>
+          <t>53790</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>13,06%</t>
         </is>
       </c>
     </row>
@@ -1289,57 +1289,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>269</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>186114</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>180593</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>433634</t>
+          <t>411833</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>138428</t>
+          <t>139560</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>80024</t>
+          <t>125168</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>164807</t>
+          <t>149493</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>75,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>87,55%</t>
+          <t>89,77%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>155196</t>
+          <t>132480</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>140945</t>
+          <t>121843</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>165751</t>
+          <t>139703</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>85,45%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>293625</t>
+          <t>272040</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>215812</t>
+          <t>254410</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>322100</t>
+          <t>283426</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,74%</t>
+          <t>88,14%</t>
         </is>
       </c>
     </row>
@@ -1519,72 +1519,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>26962</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>17029</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>41354</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>16,19%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>10,23%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>24,83%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>49821</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>23442</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>108225</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>26,47%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>12,45%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>57,49%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>27893</t>
+          <t>22558</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>17338</t>
+          <t>15335</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>42144</t>
+          <t>33195</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,23%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,89%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>77714</t>
+          <t>49520</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>49239</t>
+          <t>38134</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>155527</t>
+          <t>67150</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,26%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>41,88%</t>
+          <t>20,88%</t>
         </is>
       </c>
     </row>
@@ -1632,57 +1632,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>166522</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>223</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>188249</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>220</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>183089</t>
+          <t>155038</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>371339</t>
+          <t>321560</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1749,72 +1749,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>149237</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>141114</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>154982</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>89,81%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>84,92%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>93,27%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>216</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>150905</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>143890</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>156105</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>91,73%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>87,46%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>94,89%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>208</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>159319</t>
+          <t>150062</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>150893</t>
+          <t>142669</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>165869</t>
+          <t>154992</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>89,85%</t>
+          <t>91,51%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>85,1%</t>
+          <t>87,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>94,52%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,27 +1824,27 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>310224</t>
+          <t>299299</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>299174</t>
+          <t>288328</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>318715</t>
+          <t>307830</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,66%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>87,52%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1862,72 +1862,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>16928</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>11183</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>25051</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>10,19%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>6,73%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>15,08%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>19</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>13614</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>8414</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>20629</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>8,27%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5,11%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>12,54%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17990</t>
+          <t>13917</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11440</t>
+          <t>8987</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>26416</t>
+          <t>21310</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>14,9%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,22 +1937,22 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>31604</t>
+          <t>30845</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23113</t>
+          <t>22314</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42654</t>
+          <t>41816</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,48%</t>
+          <t>12,67%</t>
         </is>
       </c>
     </row>
@@ -1975,57 +1975,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>166165</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>235</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>164519</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>232</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>177309</t>
+          <t>163979</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>341828</t>
+          <t>330144</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2092,72 +2092,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>842</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>603352</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>582763</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>619772</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>87,85%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>84,85%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>90,24%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>830</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>566831</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>481405</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>596171</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>86,79%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>73,71%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>91,28%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>842</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>647971</t>
+          <t>558945</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>623159</t>
+          <t>544874</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>667911</t>
+          <t>570790</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>90,41%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>89,68%</t>
+          <t>92,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1214801</t>
+          <t>1162296</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1129051</t>
+          <t>1137367</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1246222</t>
+          <t>1185217</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>89,06%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>87,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>90,82%</t>
         </is>
       </c>
     </row>
@@ -2205,72 +2205,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>83472</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>67052</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>104061</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>12,15%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>9,76%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>15,15%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>85</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>86303</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>56963</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>171729</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>13,21%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>8,72%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>26,29%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>98</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>96762</t>
+          <t>59263</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>76822</t>
+          <t>47418</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>121574</t>
+          <t>73334</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>183066</t>
+          <t>142735</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>151645</t>
+          <t>119814</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>268816</t>
+          <t>167664</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>12,85%</t>
         </is>
       </c>
     </row>
@@ -2318,57 +2318,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>686824</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>915</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>653134</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>940</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>744733</t>
+          <t>618208</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1397867</t>
+          <t>1305031</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
